--- a/data/trans_orig/P80_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P80_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14270</t>
+          <t>18303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9820</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24739</t>
+          <t>30051</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>497835</t>
+          <t>540500</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489936</t>
+          <t>531196</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>501680</t>
+          <t>545733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>437463</t>
+          <t>478675</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>430422</t>
+          <t>471454</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>441922</t>
+          <t>482523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>935298</t>
+          <t>1019175</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>926240</t>
+          <t>1007103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>941159</t>
+          <t>1025727</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504206</t>
+          <t>549499</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>504206</t>
+          <t>549499</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>504206</t>
+          <t>549499</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487655</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487655</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446773</t>
+          <t>487655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>950979</t>
+          <t>1037154</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>950979</t>
+          <t>1037154</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>950979</t>
+          <t>1037154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>8237</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19185</t>
+          <t>20104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>19696</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27604</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>443062</t>
+          <t>473251</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>435305</t>
+          <t>463954</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>447572</t>
+          <t>477603</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>371866</t>
+          <t>411243</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>363237</t>
+          <t>402598</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376948</t>
+          <t>416939</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>814928</t>
+          <t>884494</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>805424</t>
+          <t>873634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>822566</t>
+          <t>891818</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>450606</t>
+          <t>481488</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>450606</t>
+          <t>481488</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>450606</t>
+          <t>481488</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382422</t>
+          <t>422702</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382422</t>
+          <t>422702</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382422</t>
+          <t>422702</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833028</t>
+          <t>904190</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833028</t>
+          <t>904190</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833028</t>
+          <t>904190</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>667286</t>
+          <t>470510</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>662049</t>
+          <t>466030</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>164750</t>
+          <t>184020</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159724</t>
+          <t>178287</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166584</t>
+          <t>186763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>832036</t>
+          <t>654530</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>826858</t>
+          <t>648616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834943</t>
+          <t>657642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>34195</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19504</t>
+          <t>22483</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47887</t>
+          <t>49303</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>41736</t>
+          <t>46586</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27014</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60462</t>
+          <t>63812</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1003914</t>
+          <t>1097648</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>986932</t>
+          <t>1082540</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1015315</t>
+          <t>1109360</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>964825</t>
+          <t>846285</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>955804</t>
+          <t>837965</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>971359</t>
+          <t>851143</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1968738</t>
+          <t>1943933</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1950012</t>
+          <t>1926707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1983460</t>
+          <t>1957686</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>975655</t>
+          <t>858676</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>975655</t>
+          <t>858676</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>975655</t>
+          <t>858676</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010474</t>
+          <t>1990519</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010474</t>
+          <t>1990519</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010474</t>
+          <t>1990519</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>18651</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>10711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24174</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>10514</t>
+          <t>12499</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>23993</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16651</t>
+          <t>20753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36073</t>
+          <t>46870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>461567</t>
+          <t>549313</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>450872</t>
+          <t>532918</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>467330</t>
+          <t>557253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>829778</t>
+          <t>817230</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>822666</t>
+          <t>809478</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>834205</t>
+          <t>822389</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1291344</t>
+          <t>1366543</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1279264</t>
+          <t>1350823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1298686</t>
+          <t>1376940</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>840292</t>
+          <t>829729</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>840292</t>
+          <t>829729</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>840292</t>
+          <t>829729</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1315337</t>
+          <t>1397693</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1315337</t>
+          <t>1397693</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1315337</t>
+          <t>1397693</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19594</t>
+          <t>19174</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19317</t>
+          <t>20426</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>230634</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>218054</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>235509</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>220913</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>240320</t>
-        </is>
-      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,27 +2588,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>758523</t>
+          <t>841207</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>755131</t>
+          <t>837713</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>759907</t>
+          <t>842674</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>994033</t>
+          <t>1071840</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>981656</t>
+          <t>1060087</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>998789</t>
+          <t>1077828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760465</t>
+          <t>843285</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760465</t>
+          <t>843285</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760465</t>
+          <t>843285</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000973</t>
+          <t>1080513</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000973</t>
+          <t>1080513</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000973</t>
+          <t>1080513</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>64274</t>
+          <t>77778</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>45820</t>
+          <t>59173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>87294</t>
+          <t>101470</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>45314</t>
+          <t>50884</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33280</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>59811</t>
+          <t>64993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>109588</t>
+          <t>128662</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88722</t>
+          <t>106130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138954</t>
+          <t>155457</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3309173</t>
+          <t>3361855</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3286153</t>
+          <t>3338163</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3327627</t>
+          <t>3380460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3527204</t>
+          <t>3578661</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3512707</t>
+          <t>3564552</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3539238</t>
+          <t>3590884</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6836377</t>
+          <t>6940515</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6807011</t>
+          <t>6913720</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6857243</t>
+          <t>6963047</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3373447</t>
+          <t>3439633</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3373447</t>
+          <t>3439633</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3373447</t>
+          <t>3439633</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3572518</t>
+          <t>3629545</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3572518</t>
+          <t>3629545</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3572518</t>
+          <t>3629545</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6945965</t>
+          <t>7069177</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6945965</t>
+          <t>7069177</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6945965</t>
+          <t>7069177</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
